--- a/artfynd/A 28723-2024 artfynd.xlsx
+++ b/artfynd/A 28723-2024 artfynd.xlsx
@@ -1164,7 +1164,7 @@
         <v>126768961</v>
       </c>
       <c r="B6" t="n">
-        <v>105396</v>
+        <v>105471</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>126769011</v>
       </c>
       <c r="B7" t="n">
-        <v>105357</v>
+        <v>105432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
